--- a/docs/assessment/templates/purview-compliance-admin-checklist.xlsx
+++ b/docs/assessment/templates/purview-compliance-admin-checklist.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purview Compliance Admin" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Purview Compliance Admin" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Purview Compliance Admin'!$A$4:$I$24</definedName>

--- a/docs/assessment/templates/purview-compliance-admin-checklist.xlsx
+++ b/docs/assessment/templates/purview-compliance-admin-checklist.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Purview Compliance Admin" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purview Compliance Admin" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Purview Compliance Admin'!$A$4:$I$24</definedName>

--- a/docs/assessment/templates/purview-compliance-admin-checklist.xlsx
+++ b/docs/assessment/templates/purview-compliance-admin-checklist.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purview Compliance Admin" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Purview Compliance Admin'!$A$4:$I$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Purview Compliance Admin'!$A$4:$I$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -513,7 +513,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Role: Purview Compliance Admin  |  FSI Copilot Governance Framework v1.8.0  |  20 controls</t>
+          <t>Role: Purview Compliance Admin  |  FSI Copilot Governance Framework v1.8.0  |  21 controls</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
     <row r="24" ht="42" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Microsoft Scout Governance</t>
+          <t>Copilot Cowork Governance</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1334,25 +1334,64 @@
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>Is Microsoft Scout governed across Frontier scope, endpoint policy plus attestation, and GitHub Copilot entitlement with documented supervision and boundary risk controls before enablement?</t>
+          <t>Is Microsoft 365 Copilot Cowork governed at GA with deliberate billing/discovery, model/browser, plugin/skill, and supervision decisions before broad enablement?</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>Frontier enrollment and scoping record for tenant and pilot groups; Intune policy export showing Scout enablement profile assignment and effective state; Admin attestation record naming approver and completion date; GitHub Copilot Business/Enterprise entitlement export matched to pilot users; Documented default permission posture for local files, shell commands, and browser actions; Autonomous-mode and unattended-automation decision records with scope constraints; Approved MCP inventory including authentication, egress, and data-path classification; Boundary map showing M365-protected data vs GitHub/local/third-party processing surfaces; Known unsupported evidence register (local automation artifacts, local MCP output, third-party inference telemetry)</t>
+          <t>Usage-based billing scope export (user/group assignments) with approver; Discovery-setting decision record and access-request workflow evidence; Model-policy record for Anthropic family and Claude Fable 5 (Preview); Cowork Browsing tenant-toggle decision tied to browser-control review; Consumption-limit policy and recent spend/consumption report; Approved plugin, uploaded package, and custom-skill inventory with owner; Purview coverage evidence (audit/eDiscovery/DLP alignment) and gap log</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr"/>
       <c r="I24" s="7" t="inlineStr"/>
     </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>4.16</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Microsoft Scout Governance</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>P4 – Operations &amp; Lifecycle</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Baseline / Recommended / Regulated</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Copilot admin center; Teams/Viva; Sentinel</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Is Microsoft Scout governed across Frontier scope, endpoint policy plus attestation, and GitHub Copilot entitlement with documented supervision and boundary risk controls before enablement?</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Frontier enrollment and scoping record for tenant and pilot groups; Intune policy export showing Scout enablement profile assignment and effective state; Admin attestation record naming approver and completion date; GitHub Copilot Business/Enterprise entitlement export matched to pilot users; Documented default permission posture for local files, shell commands, and browser actions; Autonomous-mode and unattended-automation decision records with scope constraints; Approved MCP inventory including authentication, egress, and data-path classification; Boundary map showing M365-protected data vs GitHub/local/third-party processing surfaces; Known unsupported evidence register (local automation artifacts, local MCP output, third-party inference telemetry)</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:I24"/>
+  <autoFilter ref="A4:I25"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H24" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Select Yes, Partial, or No" promptTitle="Status" prompt="Select response" type="list">
+    <dataValidation sqref="H5:H25" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Select Yes, Partial, or No" promptTitle="Status" prompt="Select response" type="list">
       <formula1>"Yes,Partial,No"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/assessment/templates/purview-compliance-admin-checklist.xlsx
+++ b/docs/assessment/templates/purview-compliance-admin-checklist.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purview Compliance Admin" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Purview Compliance Admin" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Purview Compliance Admin'!$A$4:$I$25</definedName>

--- a/docs/assessment/templates/purview-compliance-admin-checklist.xlsx
+++ b/docs/assessment/templates/purview-compliance-admin-checklist.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Purview Compliance Admin" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purview Compliance Admin" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Purview Compliance Admin'!$A$4:$I$25</definedName>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>Usage-based billing scope export (user/group assignments) with approver; Discovery-setting decision record and access-request workflow evidence; Model-policy record for Anthropic family and Claude Fable 5 (Preview); Cowork Browsing tenant-toggle decision tied to browser-control review; Consumption-limit policy and recent spend/consumption report; Approved plugin, uploaded package, and custom-skill inventory with owner; Purview coverage evidence (audit/eDiscovery/DLP alignment) and gap log</t>
+          <t>Usage-based billing scope export (user/group assignments) with approver; Current discovery-setting decision record, transition note, and access-request workflow evidence; Model-policy record for Anthropic family and any enabled provider-retention model variants; Cowork Browsing tenant-toggle decision tied to browser-control review; Consumption-limit policy plus recent Cost management and Cowork usage reports; Approved plugin, uploaded package, and custom-skill inventory with owner; Purview coverage evidence (audit/eDiscovery/DLP alignment) and gap log</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr"/>

--- a/docs/assessment/templates/purview-compliance-admin-checklist.xlsx
+++ b/docs/assessment/templates/purview-compliance-admin-checklist.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Purview Compliance Admin" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purview Compliance Admin" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Purview Compliance Admin'!$A$4:$I$25</definedName>
@@ -598,7 +598,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Sensitivity-label taxonomy document with AI-readiness review date; Labels mapped to Copilot DLP content-exclusion rules; Auto-labeling policy configuration for high-risk content types; Label usage report showing coverage across Copilot-grounded sites</t>
+          <t>Sensitivity-label taxonomy document with AI-readiness review date; Labels mapped to Copilot DLP content-exclusion rules; Auto-labeling policy configuration for high-risk content types; Content Explorer labeled-item export cross-referenced with workload inventory totals for Copilot-grounded sites, supplemented with auto-labeling policy review evidence or Activity Explorer / audit evidence for encrypted SharePoint and OneDrive items that Content Explorer doesn't surface</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Sensitivity-label taxonomy with Copilot content classification mapping; Auto-labeling policy configuration and coverage report; Label usage report from Activity Explorer for the last 30 days; Evidence of label propagation to Copilot-generated outputs</t>
+          <t>Sensitivity-label taxonomy with Copilot content classification mapping; Auto-labeling policy configuration plus Coverage by simulation context or Labeled items review evidence; Activity Explorer sensitivity-label activity for the last 30 days; Evidence of label propagation to Copilot-generated outputs</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr"/>

--- a/docs/assessment/templates/purview-compliance-admin-checklist.xlsx
+++ b/docs/assessment/templates/purview-compliance-admin-checklist.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Purview Compliance Admin" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purview Compliance Admin" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Purview Compliance Admin'!$A$4:$I$25</definedName>
@@ -754,7 +754,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Insider Risk policy configuration including Copilot indicators; Alert triage cadence and escalation path documentation; Recent alert review log (last 30 days); Integration with HR/legal escalation workflows</t>
+          <t>Insider Risk policy configuration including Generative AI apps indicators and any Risky AI usage indicators; Alert triage cadence and escalation path documentation; Recent alert review log (last 30 days), including Risky Agents coverage where applicable; Integration with HR/legal escalation workflows</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr"/>

--- a/docs/assessment/templates/purview-compliance-admin-checklist.xlsx
+++ b/docs/assessment/templates/purview-compliance-admin-checklist.xlsx
@@ -1339,7 +1339,7 @@
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>Usage-based billing scope export (user/group assignments) with approver; Discovery-setting decision record and access-request workflow evidence; Model-policy record for Anthropic family and Claude Fable 5 (Preview); Cowork Browsing tenant-toggle decision tied to browser-control review; Consumption-limit policy and recent spend/consumption report; Approved plugin, uploaded package, and custom-skill inventory with owner; Purview coverage evidence (audit/eDiscovery/DLP alignment) and gap log</t>
+          <t>Usage-based billing scope export (user/group assignments) with approver; Current discovery-setting decision record, transition note, and access-request workflow evidence; Model-policy record for Anthropic family and any enabled provider-retention model variants; Cowork Browsing tenant-toggle decision tied to browser-control review; Consumption-limit policy plus recent Cost management and Cowork usage reports; Approved plugin, uploaded package, and custom-skill inventory with owner; Purview coverage evidence (audit/eDiscovery/DLP alignment) and gap log</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr"/>

--- a/docs/assessment/templates/purview-compliance-admin-checklist.xlsx
+++ b/docs/assessment/templates/purview-compliance-admin-checklist.xlsx
@@ -754,7 +754,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Insider Risk policy configuration including Copilot indicators; Alert triage cadence and escalation path documentation; Recent alert review log (last 30 days); Integration with HR/legal escalation workflows</t>
+          <t>Insider Risk policy configuration including Generative AI apps indicators and any Risky AI usage indicators; Alert triage cadence and escalation path documentation; Recent alert review log (last 30 days), including Risky Agents coverage where applicable; Integration with HR/legal escalation workflows</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr"/>

--- a/docs/assessment/templates/purview-compliance-admin-checklist.xlsx
+++ b/docs/assessment/templates/purview-compliance-admin-checklist.xlsx
@@ -1378,7 +1378,7 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Frontier enrollment and scoping record for tenant and pilot groups; Intune policy export showing Scout enablement profile assignment and effective state; Admin attestation record naming approver and completion date; GitHub Copilot Business/Enterprise entitlement export matched to pilot users; Documented default permission posture for local files, shell commands, and browser actions; Autonomous-mode and unattended-automation decision records with scope constraints; Approved MCP inventory including authentication, egress, and data-path classification; Boundary map showing M365-protected data vs GitHub/local/third-party processing surfaces; Known unsupported evidence register (local automation artifacts, local MCP output, third-party inference telemetry)</t>
+          <t>Frontier enrollment and scoping record for tenant and pilot groups; Intune policy export showing Scout enablement profile assignment and effective state; Admin attestation record naming approver and completion date; GitHub Copilot Business/Enterprise entitlement export matched to pilot users; Documented default permission posture for local files, shell commands, and browser actions; Autonomous-mode and unattended-automation decision records with scope constraints; Approved tool-server inventory including authentication, egress, and data-path classification; Boundary map showing M365-protected data vs GitHub/local/third-party processing surfaces; Known unsupported evidence register (local automation artifacts, local tool output, third-party inference telemetry)</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr"/>
